--- a/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_zeroshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_zeroshot_cot.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -13787,7 +13787,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -16575,7 +16575,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18275,7 @@
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18836,7 +18836,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -19006,7 +19006,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19346,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21233,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -21743,7 +21743,7 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -22117,7 +22117,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22525,7 +22525,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -23239,7 +23239,7 @@
       </c>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7964028776978417</v>
+        <v>0.7769784172661871</v>
       </c>
     </row>
     <row r="3">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7483348499147935</v>
+        <v>0.7030236885558775</v>
       </c>
     </row>
     <row r="4">
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7965431138825553</v>
+        <v>0.7714998882376294</v>
       </c>
     </row>
     <row r="5">
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7720692891125445</v>
+        <v>0.7824510832212869</v>
       </c>
     </row>
     <row r="6">
@@ -24149,7 +24149,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7505490742259993</v>
+        <v>0.7003487051026618</v>
       </c>
     </row>
     <row r="7">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>355.2686876940006</v>
+        <v>781.5170808890252</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2555889839525184</v>
+        <v>0.5622425042367089</v>
       </c>
     </row>
   </sheetData>
